--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2327-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2327-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE551B2D-AF5B-4C72-9018-A60155F8037F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD4A923C-DDBE-4B4D-8945-0FA77E398A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8CD6E6C5-218C-4A17-AFC7-6AB1BF52AFDB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D4374287-5E5A-48F6-8D60-7DE0C3608DB1}"/>
   </bookViews>
   <sheets>
     <sheet name="2327-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1583,26 +1583,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{001C0D97-9CE1-454B-8379-738126C4F94C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87197EED-5B16-4F75-B841-379F026614FB}">
   <dimension ref="A1:X64"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1636,7 +1636,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1672,7 +1672,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1792,7 +1792,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2024</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="43">
         <v>2023</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="45"/>
       <c r="B13" s="46"/>
       <c r="C13" s="20" t="s">
@@ -2406,7 +2406,7 @@
       <c r="W13" s="52"/>
       <c r="X13" s="48"/>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="49" t="s">
         <v>29</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="50"/>
       <c r="B15" s="50"/>
       <c r="C15" s="22" t="s">
@@ -2508,7 +2508,7 @@
       <c r="W15" s="52"/>
       <c r="X15" s="48"/>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="41">
         <v>2022</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2021</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>29</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2020</v>
       </c>
@@ -3316,7 +3316,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2019</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>2018</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>2017</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>2016</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>2015</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>2014</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>9.59</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>2013</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>2012</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>2011</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="41">
         <v>2010</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>2009</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="41">
         <v>2008</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>2007</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="41">
         <v>2006</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>2005</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="41">
         <v>2004</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>2003</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
         <v>2002</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>2001</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="41">
         <v>2000</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>1999</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="41">
         <v>1998</v>
       </c>
@@ -5196,7 +5196,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="39">
         <v>1997</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="41">
         <v>1996</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="39">
         <v>1995</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="41">
         <v>1994</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="39">
         <v>1993</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="41">
         <v>1992</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="39">
         <v>1991</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="41">
         <v>1990</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="39">
         <v>1989</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="41">
         <v>1987</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="39">
         <v>1986</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="41" t="s">
         <v>66</v>
       </c>
